--- a/docs/shit_ABB_144_kabeli.xlsx
+++ b/docs/shit_ABB_144_kabeli.xlsx
@@ -5484,7 +5484,7 @@
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
@@ -6803,7 +6803,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="66" t="inlineStr">
         <is>
@@ -6811,7 +6810,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" s="66" t="inlineStr">
         <is>
@@ -7078,7 +7076,7 @@
     </row>
     <row r="8">
       <c r="A8" s="67" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B8" s="67" t="inlineStr">
         <is>
@@ -7308,6 +7306,7 @@
       </c>
       <c r="F15" s="60" t="inlineStr"/>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="63" t="inlineStr">
         <is>
